--- a/04_DESIGN_TABLES/DesignTable_6506.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_6506.xlsx
@@ -512,10 +512,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="C3" t="n">
-        <v>0.85</v>
+        <v>0.92</v>
       </c>
       <c r="D3" t="n">
         <v>0.5600000000000001</v>
@@ -557,7 +557,12 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Air-Way s102 only (double-pass 18 rows)</t>
+          <t>Air-Way s102 only (double-pass 18 rows); L17@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2032 = 1.260 (table had 1.19) [user 2026-10-18 A19]; L18@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2032 = 0.920 (table had 0.85) [user 2026-10-18 A19]</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>A19 (user 2026-10-18, group 2 settled): L17@DRIVE 1.19 -&gt; OMi 1.260 (Items!L2032, M038) | A19 (user 2026-10-18, group 2 settled): L18@DRIVE 0.85 -&gt; OMi 0.920 (Items!P2032, M039)</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -644,10 +649,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="C5" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="D5" t="n">
         <v>0.75</v>
@@ -689,7 +694,12 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Air-Way s102 only (double-pass 18 rows)</t>
+          <t>Air-Way s102 only (double-pass 18 rows); L17@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2033 = 1.520 (table had 1.44) [user 2026-10-18 A19]; L18@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2033 = 1.170 (table had 1.09) [user 2026-10-18 A19]</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>A19 (user 2026-10-18, group 2 settled): L17@DRIVE 1.44 -&gt; OMi 1.520 (Items!L2033, M038) | A19 (user 2026-10-18, group 2 settled): L18@DRIVE 1.09 -&gt; OMi 1.170 (Items!P2033, M039)</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -710,10 +720,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="C6" t="n">
-        <v>1.13</v>
+        <v>1.26</v>
       </c>
       <c r="D6" t="n">
         <v>0.75</v>
@@ -755,7 +765,12 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Air-Way s102 only (double-pass 18 rows)</t>
+          <t>Air-Way s102 only (double-pass 18 rows); L17@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2034 = 1.630 (table had 1.5) [user 2026-10-18 A19]; L18@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2034 = 1.260 (table had 1.13) [user 2026-10-18 A19]</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>A19 (user 2026-10-18, group 2 settled): L17@DRIVE 1.5 -&gt; OMi 1.630 (Items!L2034, M038) | A19 (user 2026-10-18, group 2 settled): L18@DRIVE 1.13 -&gt; OMi 1.260 (Items!P2034, M039)</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -842,10 +857,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.63</v>
+        <v>1.69</v>
       </c>
       <c r="C8" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="D8" t="n">
         <v>0.88</v>
@@ -887,7 +902,12 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Air-Way s102 only (double-pass 18 rows)</t>
+          <t>Air-Way s102 only (double-pass 18 rows); L17@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2036 = 1.690 (table had 1.63) [user 2026-10-18 A19]; L18@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2036 = 1.310 (table had 1.25) [user 2026-10-18 A19]</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>A19 (user 2026-10-18, group 2 settled): L17@DRIVE 1.63 -&gt; OMi 1.690 (Items!L2036, M038) | A19 (user 2026-10-18, group 2 settled): L18@DRIVE 1.25 -&gt; OMi 1.310 (Items!P2036, M039)</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -908,10 +928,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.61</v>
+        <v>1.78</v>
       </c>
       <c r="C9" t="n">
-        <v>1.19</v>
+        <v>1.36</v>
       </c>
       <c r="D9" t="n">
         <v>0.88</v>
@@ -953,7 +973,12 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Air-Way s102 only (double-pass 18 rows)</t>
+          <t>Air-Way s102 only (double-pass 18 rows); L17@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2037 = 1.780 (table had 1.61) [user 2026-10-18 A19]; L18@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2037 = 1.360 (table had 1.19) [user 2026-10-18 A19]</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>A19 (user 2026-10-18, group 2 settled): L17@DRIVE 1.61 -&gt; OMi 1.780 (Items!L2037, M038) | A19 (user 2026-10-18, group 2 settled): L18@DRIVE 1.19 -&gt; OMi 1.360 (Items!P2037, M039)</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -974,10 +999,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="C10" t="n">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="D10" t="n">
         <v>1.13</v>
@@ -1019,7 +1044,12 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Air-Way s102 only (double-pass 18 rows)</t>
+          <t>Air-Way s102 only (double-pass 18 rows); L17@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2039 = 1.920 (table had 1.87) [user 2026-10-18 A19]; L18@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2039 = 1.540 (table had 1.49) [user 2026-10-18 A19]</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>A19 (user 2026-10-18, group 2 settled): L17@DRIVE 1.87 -&gt; OMi 1.920 (Items!L2039, M038) | A19 (user 2026-10-18, group 2 settled): L18@DRIVE 1.49 -&gt; OMi 1.540 (Items!P2039, M039)</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1043,7 +1073,7 @@
         <v>1.91</v>
       </c>
       <c r="C11" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="D11" t="n">
         <v>1.13</v>
@@ -1085,7 +1115,12 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Air-Way s102 only (double-pass 18 rows)</t>
+          <t>Air-Way s102 only (double-pass 18 rows); L18@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2040 = 1.480 (table had 1.49) [user 2026-10-18 A19]</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>A19 (user 2026-10-18, group 2 settled): L18@DRIVE 1.49 -&gt; OMi 1.480 (Items!P2040, M039)</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1106,10 +1141,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="C12" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="D12" t="n">
         <v>1.13</v>
@@ -1151,7 +1186,12 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Air-Way s102 only (double-pass 18 rows)</t>
+          <t>Air-Way s102 only (double-pass 18 rows); L17@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2041 = 2.120 (table had 2.08) [user 2026-10-18 A19]; L18@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2041 = 1.620 (table had 1.58) [user 2026-10-18 A19]</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>A19 (user 2026-10-18, group 2 settled): L17@DRIVE 2.08 -&gt; OMi 2.120 (Items!L2041, M038) | A19 (user 2026-10-18, group 2 settled): L18@DRIVE 1.58 -&gt; OMi 1.620 (Items!P2041, M039)</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1238,10 +1278,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.11</v>
+        <v>2.18</v>
       </c>
       <c r="C14" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="D14" t="n">
         <v>1.38</v>
@@ -1283,7 +1323,12 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Air-Way s102 only (double-pass 18 rows)</t>
+          <t>Air-Way s102 only (double-pass 18 rows); L17@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2043 = 2.180 (table had 2.11) [user 2026-10-18 A19]; L18@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2043 = 1.680 (table had 1.62) [user 2026-10-18 A19]</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>A19 (user 2026-10-18, group 2 settled): L17@DRIVE 2.11 -&gt; OMi 2.180 (Items!L2043, M038) | A19 (user 2026-10-18, group 2 settled): L18@DRIVE 1.62 -&gt; OMi 1.680 (Items!P2043, M039)</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1656,10 +1701,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="C20" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="D20" t="n">
         <v>2.38</v>
@@ -1701,7 +1746,12 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Air-Way s102 only (double-pass 18 rows)</t>
+          <t>Air-Way s102 only (double-pass 18 rows); L17@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2049 = 3.000 (table had 2.98) [user 2026-10-18 A19]; L18@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2049 = 2.270 (table had 2.25) [user 2026-10-18 A19]</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>A19 (user 2026-10-18, group 2 settled): L17@DRIVE 2.98 -&gt; OMi 3.000 (Items!L2049, M038) | A19 (user 2026-10-18, group 2 settled): L18@DRIVE 2.25 -&gt; OMi 2.270 (Items!P2049, M039)</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">

--- a/04_DESIGN_TABLES/DesignTable_6506.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_6506.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -512,10 +512,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="C3" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="D3" t="n">
         <v>0.5600000000000001</v>
@@ -557,12 +557,12 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Air-Way s102 only (double-pass 18 rows); L17@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2032 = 1.260 (table had 1.19) [user 2026-10-18 A19]; L18@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2032 = 0.920 (table had 0.85) [user 2026-10-18 A19]</t>
+          <t>Air-Way s102 only (double-pass 18 rows); L17@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2032 = 1.260 (table had 1.19) [user 2026-10-18 A19]; L18@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2032 = 0.920 (table had 0.85) [user 2026-10-18 A19]; L17@DRIVE: Air-Way 1.19 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.26) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; L18@DRIVE: Air-Way 0.85 (raw 07_RAW_EXTRACTS; OMi file / Brennan 0.92) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 2 settled): L17@DRIVE 1.19 -&gt; OMi 1.260 (Items!L2032, M038) | A19 (user 2026-10-18, group 2 settled): L18@DRIVE 0.85 -&gt; OMi 0.920 (Items!P2032, M039)</t>
+          <t>A19 (user 2026-10-18, group 2 settled): L17@DRIVE 1.19 -&gt; OMi 1.260 (Items!L2032, M038) | A19 (user 2026-10-18, group 2 settled): L18@DRIVE 0.85 -&gt; OMi 0.920 (Items!P2032, M039) | 2026-10-20 Air-Way first: L17@DRIVE OMi/Brennan 1.26 -&gt; Air-Way 1.19 | 2026-10-20 Air-Way first: L18@DRIVE OMi/Brennan 0.92 -&gt; Air-Way 0.85</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -649,10 +649,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="C5" t="n">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="D5" t="n">
         <v>0.75</v>
@@ -694,12 +694,12 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Air-Way s102 only (double-pass 18 rows); L17@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2033 = 1.520 (table had 1.44) [user 2026-10-18 A19]; L18@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2033 = 1.170 (table had 1.09) [user 2026-10-18 A19]</t>
+          <t>Air-Way s102 only (double-pass 18 rows); L17@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2033 = 1.520 (table had 1.44) [user 2026-10-18 A19]; L18@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2033 = 1.170 (table had 1.09) [user 2026-10-18 A19]; L17@DRIVE: Air-Way 1.44 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.52) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; L18@DRIVE: Air-Way 1.09 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.17) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 2 settled): L17@DRIVE 1.44 -&gt; OMi 1.520 (Items!L2033, M038) | A19 (user 2026-10-18, group 2 settled): L18@DRIVE 1.09 -&gt; OMi 1.170 (Items!P2033, M039)</t>
+          <t>A19 (user 2026-10-18, group 2 settled): L17@DRIVE 1.44 -&gt; OMi 1.520 (Items!L2033, M038) | A19 (user 2026-10-18, group 2 settled): L18@DRIVE 1.09 -&gt; OMi 1.170 (Items!P2033, M039) | 2026-10-20 Air-Way first: L17@DRIVE OMi/Brennan 1.52 -&gt; Air-Way 1.44 | 2026-10-20 Air-Way first: L18@DRIVE OMi/Brennan 1.17 -&gt; Air-Way 1.09</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="C6" t="n">
-        <v>1.26</v>
+        <v>1.13</v>
       </c>
       <c r="D6" t="n">
         <v>0.75</v>
@@ -765,12 +765,12 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Air-Way s102 only (double-pass 18 rows); L17@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2034 = 1.630 (table had 1.5) [user 2026-10-18 A19]; L18@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2034 = 1.260 (table had 1.13) [user 2026-10-18 A19]</t>
+          <t>Air-Way s102 only (double-pass 18 rows); L17@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2034 = 1.630 (table had 1.5) [user 2026-10-18 A19]; L18@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2034 = 1.260 (table had 1.13) [user 2026-10-18 A19]; L17@DRIVE: Air-Way 1.5 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.63) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; L18@DRIVE: Air-Way 1.13 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.26) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 2 settled): L17@DRIVE 1.5 -&gt; OMi 1.630 (Items!L2034, M038) | A19 (user 2026-10-18, group 2 settled): L18@DRIVE 1.13 -&gt; OMi 1.260 (Items!P2034, M039)</t>
+          <t>A19 (user 2026-10-18, group 2 settled): L17@DRIVE 1.5 -&gt; OMi 1.630 (Items!L2034, M038) | A19 (user 2026-10-18, group 2 settled): L18@DRIVE 1.13 -&gt; OMi 1.260 (Items!P2034, M039) | 2026-10-20 Air-Way first: L17@DRIVE OMi/Brennan 1.63 -&gt; Air-Way 1.5 | 2026-10-20 Air-Way first: L18@DRIVE OMi/Brennan 1.26 -&gt; Air-Way 1.13</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.69</v>
+        <v>1.63</v>
       </c>
       <c r="C8" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="D8" t="n">
         <v>0.88</v>
@@ -902,12 +902,12 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Air-Way s102 only (double-pass 18 rows); L17@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2036 = 1.690 (table had 1.63) [user 2026-10-18 A19]; L18@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2036 = 1.310 (table had 1.25) [user 2026-10-18 A19]</t>
+          <t>Air-Way s102 only (double-pass 18 rows); L17@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2036 = 1.690 (table had 1.63) [user 2026-10-18 A19]; L18@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2036 = 1.310 (table had 1.25) [user 2026-10-18 A19]; L17@DRIVE: Air-Way 1.63 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.69) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; L18@DRIVE: Air-Way 1.25 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.31) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 2 settled): L17@DRIVE 1.63 -&gt; OMi 1.690 (Items!L2036, M038) | A19 (user 2026-10-18, group 2 settled): L18@DRIVE 1.25 -&gt; OMi 1.310 (Items!P2036, M039)</t>
+          <t>A19 (user 2026-10-18, group 2 settled): L17@DRIVE 1.63 -&gt; OMi 1.690 (Items!L2036, M038) | A19 (user 2026-10-18, group 2 settled): L18@DRIVE 1.25 -&gt; OMi 1.310 (Items!P2036, M039) | 2026-10-20 Air-Way first: L17@DRIVE OMi/Brennan 1.69 -&gt; Air-Way 1.63 | 2026-10-20 Air-Way first: L18@DRIVE OMi/Brennan 1.31 -&gt; Air-Way 1.25</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -928,10 +928,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.78</v>
+        <v>1.61</v>
       </c>
       <c r="C9" t="n">
-        <v>1.36</v>
+        <v>1.19</v>
       </c>
       <c r="D9" t="n">
         <v>0.88</v>
@@ -973,12 +973,12 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Air-Way s102 only (double-pass 18 rows); L17@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2037 = 1.780 (table had 1.61) [user 2026-10-18 A19]; L18@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2037 = 1.360 (table had 1.19) [user 2026-10-18 A19]</t>
+          <t>Air-Way s102 only (double-pass 18 rows); L17@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2037 = 1.780 (table had 1.61) [user 2026-10-18 A19]; L18@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2037 = 1.360 (table had 1.19) [user 2026-10-18 A19]; L17@DRIVE: Air-Way 1.61 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.78) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; L18@DRIVE: Air-Way 1.19 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.36) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 2 settled): L17@DRIVE 1.61 -&gt; OMi 1.780 (Items!L2037, M038) | A19 (user 2026-10-18, group 2 settled): L18@DRIVE 1.19 -&gt; OMi 1.360 (Items!P2037, M039)</t>
+          <t>A19 (user 2026-10-18, group 2 settled): L17@DRIVE 1.61 -&gt; OMi 1.780 (Items!L2037, M038) | A19 (user 2026-10-18, group 2 settled): L18@DRIVE 1.19 -&gt; OMi 1.360 (Items!P2037, M039) | 2026-10-20 Air-Way first: L17@DRIVE OMi/Brennan 1.78 -&gt; Air-Way 1.61 | 2026-10-20 Air-Way first: L18@DRIVE OMi/Brennan 1.36 -&gt; Air-Way 1.19</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -999,10 +999,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="C10" t="n">
-        <v>1.54</v>
+        <v>1.49</v>
       </c>
       <c r="D10" t="n">
         <v>1.13</v>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Air-Way s102 only (double-pass 18 rows); L17@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2039 = 1.920 (table had 1.87) [user 2026-10-18 A19]; L18@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2039 = 1.540 (table had 1.49) [user 2026-10-18 A19]</t>
+          <t>Air-Way s102 only (double-pass 18 rows); L17@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2039 = 1.920 (table had 1.87) [user 2026-10-18 A19]; L18@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2039 = 1.540 (table had 1.49) [user 2026-10-18 A19]; L17@DRIVE: Air-Way 1.87 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.92) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; L18@DRIVE: Air-Way 1.49 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.54) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 2 settled): L17@DRIVE 1.87 -&gt; OMi 1.920 (Items!L2039, M038) | A19 (user 2026-10-18, group 2 settled): L18@DRIVE 1.49 -&gt; OMi 1.540 (Items!P2039, M039)</t>
+          <t>A19 (user 2026-10-18, group 2 settled): L17@DRIVE 1.87 -&gt; OMi 1.920 (Items!L2039, M038) | A19 (user 2026-10-18, group 2 settled): L18@DRIVE 1.49 -&gt; OMi 1.540 (Items!P2039, M039) | 2026-10-20 Air-Way first: L17@DRIVE OMi/Brennan 1.92 -&gt; Air-Way 1.87 | 2026-10-20 Air-Way first: L18@DRIVE OMi/Brennan 1.54 -&gt; Air-Way 1.49</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1073,7 +1073,7 @@
         <v>1.91</v>
       </c>
       <c r="C11" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="D11" t="n">
         <v>1.13</v>
@@ -1115,12 +1115,12 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Air-Way s102 only (double-pass 18 rows); L18@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2040 = 1.480 (table had 1.49) [user 2026-10-18 A19]</t>
+          <t>Air-Way s102 only (double-pass 18 rows); L18@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2040 = 1.480 (table had 1.49) [user 2026-10-18 A19]; L18@DRIVE: Air-Way 1.49 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.48) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 2 settled): L18@DRIVE 1.49 -&gt; OMi 1.480 (Items!P2040, M039)</t>
+          <t>A19 (user 2026-10-18, group 2 settled): L18@DRIVE 1.49 -&gt; OMi 1.480 (Items!P2040, M039) | 2026-10-20 Air-Way first: L18@DRIVE OMi/Brennan 1.48 -&gt; Air-Way 1.49</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="C12" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="D12" t="n">
         <v>1.13</v>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Air-Way s102 only (double-pass 18 rows); L17@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2041 = 2.120 (table had 2.08) [user 2026-10-18 A19]; L18@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2041 = 1.620 (table had 1.58) [user 2026-10-18 A19]</t>
+          <t>Air-Way s102 only (double-pass 18 rows); L17@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2041 = 2.120 (table had 2.08) [user 2026-10-18 A19]; L18@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2041 = 1.620 (table had 1.58) [user 2026-10-18 A19]; L17@DRIVE: Air-Way 2.08 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.12) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; L18@DRIVE: Air-Way 1.58 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.62) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 2 settled): L17@DRIVE 2.08 -&gt; OMi 2.120 (Items!L2041, M038) | A19 (user 2026-10-18, group 2 settled): L18@DRIVE 1.58 -&gt; OMi 1.620 (Items!P2041, M039)</t>
+          <t>A19 (user 2026-10-18, group 2 settled): L17@DRIVE 2.08 -&gt; OMi 2.120 (Items!L2041, M038) | A19 (user 2026-10-18, group 2 settled): L18@DRIVE 1.58 -&gt; OMi 1.620 (Items!P2041, M039) | 2026-10-20 Air-Way first: L17@DRIVE OMi/Brennan 2.12 -&gt; Air-Way 2.08 | 2026-10-20 Air-Way first: L18@DRIVE OMi/Brennan 1.62 -&gt; Air-Way 1.58</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1278,10 +1278,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.18</v>
+        <v>2.11</v>
       </c>
       <c r="C14" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="D14" t="n">
         <v>1.38</v>
@@ -1323,12 +1323,12 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Air-Way s102 only (double-pass 18 rows); L17@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2043 = 2.180 (table had 2.11) [user 2026-10-18 A19]; L18@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2043 = 1.680 (table had 1.62) [user 2026-10-18 A19]</t>
+          <t>Air-Way s102 only (double-pass 18 rows); L17@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2043 = 2.180 (table had 2.11) [user 2026-10-18 A19]; L18@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2043 = 1.680 (table had 1.62) [user 2026-10-18 A19]; L17@DRIVE: Air-Way 2.11 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.18) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; L18@DRIVE: Air-Way 1.62 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.68) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 2 settled): L17@DRIVE 2.11 -&gt; OMi 2.180 (Items!L2043, M038) | A19 (user 2026-10-18, group 2 settled): L18@DRIVE 1.62 -&gt; OMi 1.680 (Items!P2043, M039)</t>
+          <t>A19 (user 2026-10-18, group 2 settled): L17@DRIVE 2.11 -&gt; OMi 2.180 (Items!L2043, M038) | A19 (user 2026-10-18, group 2 settled): L18@DRIVE 1.62 -&gt; OMi 1.680 (Items!P2043, M039) | 2026-10-20 Air-Way first: L17@DRIVE OMi/Brennan 2.18 -&gt; Air-Way 2.11 | 2026-10-20 Air-Way first: L18@DRIVE OMi/Brennan 1.68 -&gt; Air-Way 1.62</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1352,7 +1352,7 @@
         <v>2.28</v>
       </c>
       <c r="C15" t="n">
-        <v>1.72</v>
+        <v>1.57</v>
       </c>
       <c r="D15" t="n">
         <v>1.38</v>
@@ -1394,12 +1394,12 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Air-Way s102 only (double-pass 18 rows); L17@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2044 Overall Length = 2.280 (table had empty: blank on Air-Way) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L18@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2044 L 1 Size = 1.720 (table had 1.57) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; column reading: OMi Overall Length = port face to swivel-nut face (L17), L 1 = port face to stem nose / seat (L18), settled by the Brennan TFA catalog p18 6506 drawing letters L5 / L2 (Q-B-SWSTR, impact F45D); C1HEX / C3HEX / D: OMi Items!R2044 / V2044 / X2044 equal Air-Way or rounding-only (no change); TAPDRILL Air-Way - batch 15, 2026-10-02 (staged, not shipped)</t>
+          <t>Air-Way s102 only (double-pass 18 rows); L17@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2044 Overall Length = 2.280 (table had empty: blank on Air-Way) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L18@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2044 L 1 Size = 1.720 (table had 1.57) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; column reading: OMi Overall Length = port face to swivel-nut face (L17), L 1 = port face to stem nose / seat (L18), settled by the Brennan TFA catalog p18 6506 drawing letters L5 / L2 (Q-B-SWSTR, impact F45D); C1HEX / C3HEX / D: OMi Items!R2044 / V2044 / X2044 equal Air-Way or rounding-only (no change); TAPDRILL Air-Way - batch 15, 2026-10-02 (staged, not shipped); L18@DRIVE: Air-Way 1.57 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.72) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>L17: blank on Air-Way -&gt; MISSING -&gt; batch 15, 2026-10-02 (staged, not shipped): L17 = OMi Items!L2044 2.280, L18 = OMi Items!P2044 1.720 (was Air-Way 1.57) -&gt; ASSUMED; catalog TFA p18 L5 2.29 / L2 1.72 (L5 vs OMi 2.280: 0.01 inside the one source - OMi first)</t>
+          <t>L17: blank on Air-Way -&gt; MISSING -&gt; batch 15, 2026-10-02 (staged, not shipped): L17 = OMi Items!L2044 2.280, L18 = OMi Items!P2044 1.720 (was Air-Way 1.57) -&gt; ASSUMED; catalog TFA p18 L5 2.29 / L2 1.72 (L5 vs OMi 2.280: 0.01 inside the one source - OMi first) | 2026-10-20 Air-Way first: L18@DRIVE OMi/Brennan 1.72 -&gt; Air-Way 1.57</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -1562,7 +1562,7 @@
         <v>2.61</v>
       </c>
       <c r="C18" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="D18" t="n">
         <v>1.63</v>
@@ -1604,12 +1604,12 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Air-Way s102 only (double-pass 18 rows); L17@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2047 Overall Length = 2.610 (table had empty: blank on Air-Way) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L18@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2047 L 1 Size = 2.020 (table had 2.03) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; column reading: OMi Overall Length = port face to swivel-nut face (L17), L 1 = port face to stem nose / seat (L18), settled by the Brennan TFA catalog p18 6506 drawing letters L5 / L2 (Q-B-SWSTR, impact F45D); C1HEX / C3HEX / D: OMi Items!R2047 / V2047 / X2047 equal Air-Way or rounding-only (no change); TAPDRILL Air-Way - batch 15, 2026-10-02 (staged, not shipped)</t>
+          <t>Air-Way s102 only (double-pass 18 rows); L17@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2047 Overall Length = 2.610 (table had empty: blank on Air-Way) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L18@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2047 L 1 Size = 2.020 (table had 2.03) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; column reading: OMi Overall Length = port face to swivel-nut face (L17), L 1 = port face to stem nose / seat (L18), settled by the Brennan TFA catalog p18 6506 drawing letters L5 / L2 (Q-B-SWSTR, impact F45D); C1HEX / C3HEX / D: OMi Items!R2047 / V2047 / X2047 equal Air-Way or rounding-only (no change); TAPDRILL Air-Way - batch 15, 2026-10-02 (staged, not shipped); L18@DRIVE: Air-Way 2.03 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.02) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>L17: blank on Air-Way -&gt; MISSING -&gt; batch 15, 2026-10-02 (staged, not shipped): L17 = OMi Items!L2047 2.610, L18 = OMi Items!P2047 2.020 (was Air-Way 2.03) -&gt; ASSUMED; catalog TFA p18 L5 2.614 / L2 2.02 (2.614 vs OMi 2.610: rounding only)</t>
+          <t>L17: blank on Air-Way -&gt; MISSING -&gt; batch 15, 2026-10-02 (staged, not shipped): L17 = OMi Items!L2047 2.610, L18 = OMi Items!P2047 2.020 (was Air-Way 2.03) -&gt; ASSUMED; catalog TFA p18 L5 2.614 / L2 2.02 (2.614 vs OMi 2.610: rounding only) | 2026-10-20 Air-Way first: L18@DRIVE OMi/Brennan 2.02 -&gt; Air-Way 2.03</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -1633,7 +1633,7 @@
         <v>2.83</v>
       </c>
       <c r="C19" t="n">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="D19" t="n">
         <v>2</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Air-Way s102 only (double-pass 18 rows); L17@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2048 Overall Length = 2.830 (table had empty: blank on Air-Way) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L18@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2048 L 1 Size = 2.200 (table had 2.13) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; column reading: OMi Overall Length = port face to swivel-nut face (L17), L 1 = port face to stem nose / seat (L18), settled by the Brennan TFA catalog p18 6506 drawing letters L5 / L2 (Q-B-SWSTR, impact F45D); C1HEX / C3HEX / D: OMi Items!R2048 / V2048 / X2048 equal Air-Way or rounding-only (no change); TAPDRILL Air-Way - batch 15, 2026-10-02 (staged, not shipped)</t>
+          <t>Air-Way s102 only (double-pass 18 rows); L17@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2048 Overall Length = 2.830 (table had empty: blank on Air-Way) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L18@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2048 L 1 Size = 2.200 (table had 2.13) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; column reading: OMi Overall Length = port face to swivel-nut face (L17), L 1 = port face to stem nose / seat (L18), settled by the Brennan TFA catalog p18 6506 drawing letters L5 / L2 (Q-B-SWSTR, impact F45D); C1HEX / C3HEX / D: OMi Items!R2048 / V2048 / X2048 equal Air-Way or rounding-only (no change); TAPDRILL Air-Way - batch 15, 2026-10-02 (staged, not shipped); L18@DRIVE: Air-Way 2.13 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.2) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>L17: blank on Air-Way -&gt; MISSING -&gt; batch 15, 2026-10-02 (staged, not shipped): L17 = OMi Items!L2048 2.830, L18 = OMi Items!P2048 2.200 (was Air-Way 2.13) -&gt; ASSUMED; catalog TFA p18 L5 2.825 / L2 2.200 (2.825 vs OMi 2.830: rounding only)</t>
+          <t>L17: blank on Air-Way -&gt; MISSING -&gt; batch 15, 2026-10-02 (staged, not shipped): L17 = OMi Items!L2048 2.830, L18 = OMi Items!P2048 2.200 (was Air-Way 2.13) -&gt; ASSUMED; catalog TFA p18 L5 2.825 / L2 2.200 (2.825 vs OMi 2.830: rounding only) | 2026-10-20 Air-Way first: L18@DRIVE OMi/Brennan 2.2 -&gt; Air-Way 2.13</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -1701,10 +1701,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="C20" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="D20" t="n">
         <v>2.38</v>
@@ -1746,12 +1746,12 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Air-Way s102 only (double-pass 18 rows); L17@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2049 = 3.000 (table had 2.98) [user 2026-10-18 A19]; L18@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2049 = 2.270 (table had 2.25) [user 2026-10-18 A19]</t>
+          <t>Air-Way s102 only (double-pass 18 rows); L17@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2049 = 3.000 (table had 2.98) [user 2026-10-18 A19]; L18@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2049 = 2.270 (table had 2.25) [user 2026-10-18 A19]; L17@DRIVE: Air-Way 2.98 (raw 07_RAW_EXTRACTS; OMi file / Brennan 3) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; L18@DRIVE: Air-Way 2.25 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.27) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 2 settled): L17@DRIVE 2.98 -&gt; OMi 3.000 (Items!L2049, M038) | A19 (user 2026-10-18, group 2 settled): L18@DRIVE 2.25 -&gt; OMi 2.270 (Items!P2049, M039)</t>
+          <t>A19 (user 2026-10-18, group 2 settled): L17@DRIVE 2.98 -&gt; OMi 3.000 (Items!L2049, M038) | A19 (user 2026-10-18, group 2 settled): L18@DRIVE 2.25 -&gt; OMi 2.270 (Items!P2049, M039) | 2026-10-20 Air-Way first: L17@DRIVE OMi/Brennan 3 -&gt; Air-Way 2.98 | 2026-10-20 Air-Way first: L18@DRIVE OMi/Brennan 2.27 -&gt; Air-Way 2.25</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">

--- a/04_DESIGN_TABLES/DesignTable_6506.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_6506.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1771,24 +1771,58 @@
           <t>6506-06-04</t>
         </is>
       </c>
+      <c r="B21" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.172</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>1/4</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr">
         <is>
           <t>6506-06-04</t>
         </is>
       </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>3/8-18 (A NPTF) x 7/16-20 (B UN/UNF-2B)</t>
+        </is>
+      </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-20 batch-19 stage A_answered (not shipped): L17 / L18 / hex / nut hex / D = OMi WebsitePartsInfo2026.xlsx Items row 2035; column reading L17 = OMi "Overall Length" (port face to the swivel-nut face), L18 = OMi "L 1" (to the seat) - Q-B-SWSTR, settled by the Brennan TFA p18 letters L5 / L2 (batch 15); tap drill 0.57 = Air-Way per size (A1); thread majors from the end library; cross-check Brennan TFA p18 6506-06-04: L5 1.59 / L2 1.24 / C4 HEX 0.875 / C HEX 0.563 / A DRILL 0.172 - equal or rounding; no $PRP@DimSource column in this table - source = OMI</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | 2026-10-20 batch-19 stage A_answered (not shipped): filled from OMi Items row 2035 + A1 tap drill; cross-check Brennan TFA p18 6506-06-04: L5 1.59 / L2 1.24 / C4 HEX 0.875 / C HEX 0.563 / A DRILL 0.172 - equal or rounding</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -1808,24 +1842,58 @@
           <t>6506-06-10</t>
         </is>
       </c>
+      <c r="B22" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.9379999999999999</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.484</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>5/8</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr">
         <is>
           <t>6506-06-10</t>
         </is>
       </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>3/8-18 (A NPTF) x 7/8-14 (B UN/UNF-2B)</t>
+        </is>
+      </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-20 batch-19 stage A_answered (not shipped): L17 / L18 / hex / nut hex / D = OMi WebsitePartsInfo2026.xlsx Items row 2038; column reading L17 = OMi "Overall Length" (port face to the swivel-nut face), L18 = OMi "L 1" (to the seat) - Q-B-SWSTR, settled by the Brennan TFA p18 letters L5 / L2 (batch 15); tap drill 0.57 = Air-Way per size (A1); thread majors from the end library; OMi Side 1 Thread prints "1/2- 14 NPTF" - a misprint: its own Side 1 Size " 3/8 ", the part number -06 and Brennan p18 (3/8-18) give 3/8-18 (Q-THREAD: the part number's thread); cross-check Brennan TFA p18 6506-06-10: L5 1.900 / L2 1.400 / C4 HEX 0.938 / C HEX 1.000 / A DRILL 0.484 - equal; no $PRP@DimSource column in this table - source = OMI</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | 2026-10-20 batch-19 stage A_answered (not shipped): filled from OMi Items row 2038 + A1 tap drill; cross-check Brennan TFA p18 6506-06-10: L5 1.900 / L2 1.400 / C4 HEX 0.938 / C HEX 1.000 / A DRILL 0.484 - equal | OMi thread text misprint (1/2-14) - 3/8-18 used</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -1845,24 +1913,58 @@
           <t>6506-12-08</t>
         </is>
       </c>
+      <c r="B23" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.391</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>1/2</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr">
         <is>
           <t>6506-12-08</t>
         </is>
       </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>3/4-14 (A NPTF) x 3/4-16 (B UN/UNF-2B)</t>
+        </is>
+      </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-20 batch-19 stage A_answered (not shipped): L17 / L18 / hex / nut hex / D = OMi WebsitePartsInfo2026.xlsx Items row 2042; column reading L17 = OMi "Overall Length" (port face to the swivel-nut face), L18 = OMi "L 1" (to the seat) - Q-B-SWSTR, settled by the Brennan TFA p18 letters L5 / L2 (batch 15); tap drill 0.91 = Air-Way per size (A1); thread majors from the end library; not printed in the Brennan TFA catalog; no $PRP@DimSource column in this table - source = OMI</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | 2026-10-20 batch-19 stage A_answered (not shipped): filled from OMi Items row 2042 + A1 tap drill; not printed in the Brennan TFA catalog</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
